--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="536" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="560" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="560" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="584" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="584" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="624" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="624" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="640" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="640" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="648" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="648" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="680" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="680" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="720" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="720" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="736" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="736" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="752" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="752" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="768" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="768" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="784" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="784" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="792" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="792" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="800" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="800" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="816" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="816" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="824" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="824" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="832" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="832" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="840" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="840" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="864" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="864" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="888" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="888" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="904" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
+++ b/outputs/build/diagnostics/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="904" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="936" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>
